--- a/tasks/finalpool/yt-fireship-tech-report-excel-notion/groundtruth_workspace/Tech_Trend_Report.xlsx
+++ b/tasks/finalpool/yt-fireship-tech-report-excel-notion/groundtruth_workspace/Tech_Trend_Report.xlsx
@@ -457,120 +457,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dQw4w9WgXcQ</t>
+          <t>Nl7aCUsWykg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100 Seconds of Code: JavaScript</t>
+          <t>Big Tech in panic mode... Did DeepSeek R1 just pop the AI bubble?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>216</v>
       </c>
       <c r="E2" t="n">
-        <v>2850000</v>
+        <v>3878491</v>
       </c>
       <c r="F2" t="n">
-        <v>62000</v>
+        <v>152669</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>s2skans2dP4</t>
+          <t>-2k1rcRzsLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TypeScript in 100 Seconds</t>
+          <t>This free Chinese AI just crushed OpenAI's $200 o1 model...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="E3" t="n">
-        <v>2400000</v>
+        <v>3115193</v>
       </c>
       <c r="F3" t="n">
-        <v>55000</v>
+        <v>90213</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tn6-PIqc4UM</t>
+          <t>LKCVKw9CzFo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>React in 100 Seconds</t>
+          <t>100+ Linux Things you Need to Know</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>118</v>
+        <v>742</v>
       </c>
       <c r="E4" t="n">
-        <v>2100000</v>
+        <v>2891861</v>
       </c>
       <c r="F4" t="n">
-        <v>48000</v>
+        <v>107006</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aircAruvnKk</t>
+          <t>Iq_r7IcNmUk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI is Eating the World - But What Does It Actually Do?</t>
+          <t>25 crazy software bugs explained</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>540</v>
+        <v>1009</v>
       </c>
       <c r="E5" t="n">
-        <v>1950000</v>
+        <v>2496715</v>
       </c>
       <c r="F5" t="n">
-        <v>41000</v>
+        <v>72881</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -581,182 +581,182 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5C_HPTJg55E</t>
+          <t>4yDm6xNeYas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rust in 100 Seconds</t>
+          <t>Some bad code just broke a billion Windows machines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="E6" t="n">
-        <v>1800000</v>
+        <v>2467547</v>
       </c>
       <c r="F6" t="n">
-        <v>43000</v>
+        <v>121950</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Software Engineering</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rfscVS0vtbw</t>
+          <t>hpwoGjpYygI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Python in 100 Seconds</t>
+          <t>DeepSeek stole our tech... says OpenAI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="E7" t="n">
-        <v>1650000</v>
+        <v>2436569</v>
       </c>
       <c r="F7" t="n">
-        <v>38000</v>
+        <v>92019</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ysEN5RaKOlA</t>
+          <t>jwnez8HdN7E</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CSS in 100 Seconds</t>
+          <t>Microsoft’s new chip looks like science fiction…</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="E8" t="n">
-        <v>1500000</v>
+        <v>2329914</v>
       </c>
       <c r="F8" t="n">
-        <v>34000</v>
+        <v>71310</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Web Dev</t>
+          <t>Big Tech</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FHZKLx3ruC8</t>
+          <t>N3ZGNT5S5IU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Docker in 100 Seconds</t>
+          <t>Hackers are destroying the Internet's history book right now</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>110</v>
+        <v>261</v>
       </c>
       <c r="E9" t="n">
-        <v>1350000</v>
+        <v>1927279</v>
       </c>
       <c r="F9" t="n">
-        <v>31000</v>
+        <v>107099</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gPP7sdhxB7M</t>
+          <t>x2WtHZciC74</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Next.js in 100 Seconds</t>
+          <t>Claude 3.7 goes hard for programmers…</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>348</v>
       </c>
       <c r="E10" t="n">
-        <v>1200000</v>
+        <v>1926147</v>
       </c>
       <c r="F10" t="n">
-        <v>28000</v>
+        <v>80601</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I6ypD4nkynU</t>
+          <t>Tw18-4U7mts</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Machine Learning in 100 Seconds</t>
+          <t>The "vibe coding" mind virus explained…</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>121</v>
+        <v>286</v>
       </c>
       <c r="E11" t="n">
-        <v>980000</v>
+        <v>1846051</v>
       </c>
       <c r="F11" t="n">
-        <v>22000</v>
+        <v>65631</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,129 +803,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>AI/ML</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>2850000</v>
+        <v>15699166</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2400000</v>
+        <v>2891861</v>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3300000</v>
+        <v>2467547</v>
       </c>
       <c r="D4" t="n">
-        <v>117.5</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML</t>
+          <t>Big Tech</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2930000</v>
+        <v>2329914</v>
       </c>
       <c r="D5" t="n">
-        <v>330.5</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1800000</v>
+        <v>1927279</v>
       </c>
       <c r="D6" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Web Dev</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="D9" t="n">
-        <v>110</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
